--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/3042-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/3042-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5BEF9A15-46B5-4CB2-8521-5430D220ED30}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{794AD020-2D9E-4A45-B7B0-E5506C523E4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{33495880-A822-4CEE-93C0-697F28C25C5F}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{58BE172D-59E7-4DD2-BFDC-216C66C551D8}"/>
   </bookViews>
   <sheets>
     <sheet name="3042-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1430,25 +1430,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CE0D2D2-484C-4C14-9B94-3C910B9954E6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C5DCEE41-728E-464F-B37C-E7D3439BFC2F}">
   <dimension ref="A1:R34"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="7.33203125" customWidth="1"/>
-    <col min="3" max="3" width="8" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="7" width="8.33203125" customWidth="1"/>
-    <col min="8" max="8" width="8" customWidth="1"/>
-    <col min="9" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.88671875" customWidth="1"/>
+    <col min="1" max="1" width="6.5" customWidth="1"/>
+    <col min="2" max="2" width="9.25" customWidth="1"/>
+    <col min="3" max="3" width="10" customWidth="1"/>
+    <col min="4" max="4" width="10.5" customWidth="1"/>
+    <col min="5" max="5" width="10" customWidth="1"/>
+    <col min="6" max="7" width="10.5" customWidth="1"/>
+    <col min="8" max="8" width="10" customWidth="1"/>
+    <col min="9" max="10" width="10.5" customWidth="1"/>
+    <col min="11" max="13" width="10" customWidth="1"/>
+    <col min="14" max="14" width="10.5" customWidth="1"/>
+    <col min="15" max="17" width="10" customWidth="1"/>
+    <col min="18" max="18" width="10.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="20" t="s">
         <v>0</v>
       </c>
@@ -1476,7 +1476,7 @@
       <c r="Q1" s="29"/>
       <c r="R1" s="21"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="22" t="s">
         <v>1</v>
       </c>
@@ -1506,7 +1506,7 @@
       <c r="Q2" s="31"/>
       <c r="R2" s="32"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
         <v>2</v>
       </c>
@@ -1552,7 +1552,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="24"/>
       <c r="B4" s="25"/>
       <c r="C4" s="7"/>
@@ -1602,7 +1602,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="36">
         <v>2025</v>
       </c>
@@ -1656,7 +1656,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1712,7 +1712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1768,7 +1768,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="38">
         <v>2024</v>
       </c>
@@ -1822,7 +1822,7 @@
         <v>3.9</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="36">
         <v>2023</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>7.28</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="38">
         <v>2022</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>8.25</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="36">
         <v>2021</v>
       </c>
@@ -1984,7 +1984,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="38">
         <v>2020</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="36">
         <v>2019</v>
       </c>
@@ -2092,7 +2092,7 @@
         <v>5.0599999999999996</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="38">
         <v>2018</v>
       </c>
@@ -2146,7 +2146,7 @@
         <v>6.67</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="36">
         <v>2017</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>6.59</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="38">
         <v>2016</v>
       </c>
@@ -2254,7 +2254,7 @@
         <v>5.66</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="36">
         <v>2015</v>
       </c>
@@ -2308,7 +2308,7 @@
         <v>7.35</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="38">
         <v>2014</v>
       </c>
@@ -2362,7 +2362,7 @@
         <v>5.22</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="36">
         <v>2013</v>
       </c>
@@ -2416,7 +2416,7 @@
         <v>5.31</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="38">
         <v>2012</v>
       </c>
@@ -2470,7 +2470,7 @@
         <v>4.45</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="36">
         <v>2011</v>
       </c>
@@ -2524,7 +2524,7 @@
         <v>5.62</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="38">
         <v>2010</v>
       </c>
@@ -2578,7 +2578,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="36">
         <v>2009</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="38">
         <v>2008</v>
       </c>
@@ -2686,7 +2686,7 @@
         <v>5.05</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="36">
         <v>2007</v>
       </c>
@@ -2740,7 +2740,7 @@
         <v>3.91</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="38">
         <v>2006</v>
       </c>
@@ -2794,7 +2794,7 @@
         <v>3.23</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="36">
         <v>2005</v>
       </c>
@@ -2848,7 +2848,7 @@
         <v>4.47</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="38">
         <v>2004</v>
       </c>
@@ -2902,7 +2902,7 @@
         <v>4.82</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="36">
         <v>2003</v>
       </c>
@@ -2956,7 +2956,7 @@
         <v>2.76</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="38">
         <v>2002</v>
       </c>
@@ -3010,7 +3010,7 @@
         <v>7.61</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="36">
         <v>2001</v>
       </c>
@@ -3064,7 +3064,7 @@
         <v>4.1399999999999997</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="38">
         <v>2000</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="36">
         <v>1999</v>
       </c>
@@ -3172,7 +3172,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="38" t="s">
         <v>30</v>
       </c>
